--- a/history/swing_picks.xlsx
+++ b/history/swing_picks.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -940,7 +940,7 @@
         <v>4869</v>
       </c>
       <c r="L6" t="n">
-        <v>4879.87</v>
+        <v>4879.88</v>
       </c>
       <c r="M6" t="n">
         <v>4560.6</v>
@@ -1362,6 +1362,786 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4254.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4268.26</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3953.37</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4740.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5212.94</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>571</v>
+      </c>
+      <c r="L13" t="n">
+        <v>572.5700000000001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>537.42</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="O13" t="n">
+        <v>625.3099999999999</v>
+      </c>
+      <c r="P13" t="n">
+        <v>678.04</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1715</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1716.71</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1540.76</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1980.65</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2244.58</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>160</v>
+      </c>
+      <c r="L15" t="n">
+        <v>160.24</v>
+      </c>
+      <c r="M15" t="n">
+        <v>150.22</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="O15" t="n">
+        <v>175.28</v>
+      </c>
+      <c r="P15" t="n">
+        <v>190.31</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1411.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1424.22</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1303.18</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1605.79</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1787.36</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="M17" t="n">
+        <v>79.29000000000001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4869</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4879.88</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4560.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5358.79</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5837.7</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TEGA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1993.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2020.32</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1841.42</v>
+      </c>
+      <c r="N19" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2288.66</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2557.01</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>326.75</v>
+      </c>
+      <c r="L20" t="n">
+        <v>327.08</v>
+      </c>
+      <c r="M20" t="n">
+        <v>301.23</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>365.85</v>
+      </c>
+      <c r="P20" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" s="2" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22090</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1226.7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1236.64</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1192.66</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1302.59</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1368.55</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" s="2" t="n">
         <v>46308</v>
       </c>
     </row>
@@ -1402,7 +2182,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1412,7 +2192,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">

--- a/history/swing_picks.xlsx
+++ b/history/swing_picks.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -435,20 +435,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="7" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
   </cols>
@@ -649,7 +649,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -660,7 +660,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="3">
@@ -727,18 +727,28 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T3" t="n">
+        <v>160.24</v>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="Z3" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="4">
@@ -805,18 +815,28 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1718.5</v>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.174</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-1.8</v>
+      </c>
       <c r="Z4" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="5">
@@ -883,7 +903,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -894,7 +914,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="6">
@@ -961,18 +981,28 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4879.88</v>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.89</v>
+      </c>
       <c r="Z6" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7">
@@ -1039,7 +1069,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1050,7 +1080,7 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="8">
@@ -1117,7 +1147,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1128,7 +1158,7 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="9">
@@ -1195,18 +1225,28 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1289.09</v>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.65</v>
+      </c>
       <c r="Z9" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="10">
@@ -1273,18 +1313,28 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1904.5</v>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.097</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="Z10" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="11">
@@ -1351,18 +1401,28 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3406.6</v>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.297</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-1.63</v>
+      </c>
       <c r="Z11" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="12">
@@ -1429,18 +1489,28 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4268.26</v>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.516</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-3.81</v>
+      </c>
       <c r="Z12" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="13">
@@ -1507,7 +1577,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1518,7 +1588,7 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="14">
@@ -1585,18 +1655,28 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1718.5</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.174</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.8</v>
+      </c>
       <c r="Z14" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="15">
@@ -1663,18 +1743,28 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T15" t="n">
+        <v>160.24</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="Z15" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="16">
@@ -1741,18 +1831,28 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1424.22</v>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.38</v>
+      </c>
       <c r="Z16" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="17">
@@ -1819,7 +1919,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
@@ -1830,7 +1930,7 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="18">
@@ -1897,18 +1997,28 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4879.88</v>
+      </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.89</v>
+      </c>
       <c r="Z18" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="19">
@@ -1975,7 +2085,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>not triggered</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -1986,7 +2096,7 @@
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="20">
@@ -2053,18 +2163,28 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T20" t="n">
+        <v>327.08</v>
+      </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-1.31</v>
+      </c>
       <c r="Z20" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="21">
@@ -2131,18 +2251,3648 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1236.64</v>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.681</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-2.42</v>
+      </c>
       <c r="Z21" s="2" t="n">
-        <v>46308</v>
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4554.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4617.61</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4386.18</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4964.76</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5311.91</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>20170</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20369.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>19455.73</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="O23" t="n">
+        <v>21739.77</v>
+      </c>
+      <c r="P23" t="n">
+        <v>23110.19</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1364</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1365.36</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1228.81</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1570.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1775.03</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1365.36</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1318.4</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1326.22</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1196.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1520.36</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1714.5</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>805.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>807.26</v>
+      </c>
+      <c r="M26" t="n">
+        <v>768.33</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="O26" t="n">
+        <v>865.64</v>
+      </c>
+      <c r="P26" t="n">
+        <v>924.03</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2664.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2717.82</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2561.65</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2952.06</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3186.3</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>401.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>411.91</v>
+      </c>
+      <c r="M28" t="n">
+        <v>373.96</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="O28" t="n">
+        <v>468.83</v>
+      </c>
+      <c r="P28" t="n">
+        <v>525.75</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1938</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1943.94</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1866.54</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2060.04</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2176.14</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1843.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1849.85</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1751.24</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1997.76</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2145.67</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1849.85</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>807</v>
+      </c>
+      <c r="L31" t="n">
+        <v>824.5700000000001</v>
+      </c>
+      <c r="M31" t="n">
+        <v>768.65</v>
+      </c>
+      <c r="N31" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="O31" t="n">
+        <v>908.46</v>
+      </c>
+      <c r="P31" t="n">
+        <v>992.35</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CRAFTSMAN</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10997</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11037.03</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9882.93</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="O32" t="n">
+        <v>12768.17</v>
+      </c>
+      <c r="P32" t="n">
+        <v>14499.3</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T32" t="n">
+        <v>11037.03</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4554.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4617.61</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4386.18</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4964.76</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5311.91</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F34" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20170</v>
+      </c>
+      <c r="L34" t="n">
+        <v>20369.35</v>
+      </c>
+      <c r="M34" t="n">
+        <v>19455.73</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="O34" t="n">
+        <v>21739.77</v>
+      </c>
+      <c r="P34" t="n">
+        <v>23110.19</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22038</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>FLUOROCHEM</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4632.1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4684.68</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4373.04</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5152.14</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5619.6</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>not triggered</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>21</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="M36" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>354.68</v>
+      </c>
+      <c r="P36" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T36" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1062.95</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1073.27</v>
+      </c>
+      <c r="M37" t="n">
+        <v>992.09</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1195.05</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1316.83</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1074.1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>-0.247</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>21</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>160.66</v>
+      </c>
+      <c r="L38" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="M38" t="n">
+        <v>150.24</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="O38" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="P38" t="n">
+        <v>200.34</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T38" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>21</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1917.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1935.93</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1778.25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2172.46</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2408.98</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>338.4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="M40" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>354.68</v>
+      </c>
+      <c r="P40" t="n">
+        <v>369.96</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T40" t="n">
+        <v>339.39</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2142.6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2147.14</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2002.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2364.71</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2582.28</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2147.14</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CEMPRO</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1221.4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1270.07</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1096.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1530.42</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1790.77</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1062.95</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1073.27</v>
+      </c>
+      <c r="M43" t="n">
+        <v>992.09</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1195.05</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1316.83</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1074.1</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>-0.247</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>56</v>
+      </c>
+      <c r="K44" t="n">
+        <v>160.66</v>
+      </c>
+      <c r="L44" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="M44" t="n">
+        <v>150.24</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="O44" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="P44" t="n">
+        <v>200.34</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T44" t="n">
+        <v>162.76</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="X44" t="n">
+        <v>-0.266</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>295.5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>286.64</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>308.78</v>
+      </c>
+      <c r="P45" t="n">
+        <v>322.07</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Oil Gas &amp; Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="K46" t="n">
+        <v>505.05</v>
+      </c>
+      <c r="L46" t="n">
+        <v>508.21</v>
+      </c>
+      <c r="M46" t="n">
+        <v>454.74</v>
+      </c>
+      <c r="N46" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="O46" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>668.6</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="T46" t="n">
+        <v>508.21</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>-0.131</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ZENTEC</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1695</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1710.11</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1524.92</v>
+      </c>
+      <c r="N47" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1987.88</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2265.66</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>9</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>36</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1917.2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1935.93</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1778.25</v>
+      </c>
+      <c r="N48" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2172.46</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2408.98</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4473.4</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4491.99</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4288.16</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4797.72</v>
+      </c>
+      <c r="P49" t="n">
+        <v>5103.46</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="K50" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="L50" t="n">
+        <v>439.94</v>
+      </c>
+      <c r="M50" t="n">
+        <v>422.34</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" t="n">
+        <v>466.33</v>
+      </c>
+      <c r="P50" t="n">
+        <v>492.73</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="K51" t="n">
+        <v>345</v>
+      </c>
+      <c r="L51" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="M51" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="O51" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="P51" t="n">
+        <v>395.36</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>20011</v>
+      </c>
+      <c r="L52" t="n">
+        <v>20261.24</v>
+      </c>
+      <c r="M52" t="n">
+        <v>19675.93</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O52" t="n">
+        <v>21139.2</v>
+      </c>
+      <c r="P52" t="n">
+        <v>22017.17</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G53" t="n">
+        <v>5</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>58</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2152.7</v>
+      </c>
+      <c r="L53" t="n">
+        <v>2166.16</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2094.13</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2274.22</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2382.27</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4095.1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>4114.11</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3793.72</v>
+      </c>
+      <c r="N54" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4594.69</v>
+      </c>
+      <c r="P54" t="n">
+        <v>5075.27</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G55" t="n">
+        <v>7</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1365.9</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1384.68</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1249.98</v>
+      </c>
+      <c r="N55" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1586.74</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1788.8</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>nifty200</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>breakout</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K56" t="n">
+        <v>200.85</v>
+      </c>
+      <c r="L56" t="n">
+        <v>204.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>189.09</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O56" t="n">
+        <v>226.87</v>
+      </c>
+      <c r="P56" t="n">
+        <v>249.55</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>78</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4473.4</v>
+      </c>
+      <c r="L57" t="n">
+        <v>4491.99</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4288.16</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4797.72</v>
+      </c>
+      <c r="P57" t="n">
+        <v>5103.46</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CARTRADE</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3011.4</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3028.03</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2846.23</v>
+      </c>
+      <c r="N58" t="n">
+        <v>6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3300.71</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3573.4</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="L59" t="n">
+        <v>439.94</v>
+      </c>
+      <c r="M59" t="n">
+        <v>422.34</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>466.33</v>
+      </c>
+      <c r="P59" t="n">
+        <v>492.73</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="K60" t="n">
+        <v>345</v>
+      </c>
+      <c r="L60" t="n">
+        <v>345.75</v>
+      </c>
+      <c r="M60" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="O60" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="P60" t="n">
+        <v>395.36</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="K61" t="n">
+        <v>615.4</v>
+      </c>
+      <c r="L61" t="n">
+        <v>619.12</v>
+      </c>
+      <c r="M61" t="n">
+        <v>576.86</v>
+      </c>
+      <c r="N61" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="O61" t="n">
+        <v>682.51</v>
+      </c>
+      <c r="P61" t="n">
+        <v>745.9</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2159.7</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2164.96</v>
+      </c>
+      <c r="M62" t="n">
+        <v>2003.86</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="O62" t="n">
+        <v>2406.62</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2648.28</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G63" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3206</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3222.22</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3033.65</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3505.07</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3787.91</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G64" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>GESHIP</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>64</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1507.4</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1516.92</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1448.37</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1619.73</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1722.54</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G65" t="n">
+        <v>9</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LLOYDSME</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1851.7</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1876.88</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1777.19</v>
+      </c>
+      <c r="N65" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2026.4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2175.93</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" s="2" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nifty500</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>unfavourable</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="G66" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pullback</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="K66" t="n">
+        <v>20011</v>
+      </c>
+      <c r="L66" t="n">
+        <v>20261.24</v>
+      </c>
+      <c r="M66" t="n">
+        <v>19675.93</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O66" t="n">
+        <v>21139.2</v>
+      </c>
+      <c r="P66" t="n">
+        <v>22017.17</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" s="2" t="n">
+        <v>46311</v>
       </c>
     </row>
   </sheetData>
@@ -2182,7 +5932,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -2192,7 +5942,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2202,7 +5952,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +5962,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
